--- a/data/trans_dic/IP09-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,61</t>
+          <t>0,0; 35,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,75; 63,95</t>
+          <t>9,66; 63,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,25</t>
+          <t>0,0; 58,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,76; 70,86</t>
+          <t>22,11; 69,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,21; 56,93</t>
+          <t>11,16; 52,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,26</t>
+          <t>0,0; 54,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,01; 90,3</t>
+          <t>35,75; 91,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 44,29</t>
+          <t>6,05; 47,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,19; 38,33</t>
+          <t>9,3; 39,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 49,01</t>
+          <t>9,74; 48,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,09; 65,84</t>
+          <t>20,52; 66,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,13; 47,82</t>
+          <t>18,76; 48,68</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 53,02</t>
+          <t>6,8; 52,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,01; 59,2</t>
+          <t>8,78; 59,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,83; 64,02</t>
+          <t>9,57; 63,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,18</t>
+          <t>0,0; 36,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,94; 77,03</t>
+          <t>28,77; 77,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,76; 63,44</t>
+          <t>10,37; 66,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 39,53</t>
+          <t>4,32; 35,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 35,1</t>
+          <t>4,12; 34,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,22; 83,57</t>
+          <t>39,46; 83,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,55; 54,73</t>
+          <t>13,97; 52,71</t>
         </is>
       </c>
     </row>
@@ -996,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,42; 57,79</t>
+          <t>7,69; 57,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1016,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,95; 50,0</t>
+          <t>13,97; 53,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,68</t>
+          <t>0,0; 26,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,95; 69,91</t>
+          <t>10,56; 68,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 62,47</t>
+          <t>6,85; 64,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,62; 42,56</t>
+          <t>10,99; 42,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 28,62</t>
+          <t>3,17; 28,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,02; 71,85</t>
+          <t>22,08; 73,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,9; 57,39</t>
+          <t>8,43; 55,74</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,77; 47,52</t>
+          <t>13,83; 46,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,63; 47,51</t>
+          <t>21,47; 48,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,3; 47,46</t>
+          <t>11,12; 46,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,93; 72,49</t>
+          <t>14,0; 76,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,84; 43,25</t>
+          <t>9,96; 40,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,96; 60,93</t>
+          <t>34,29; 62,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,99; 64,54</t>
+          <t>18,83; 66,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,81; 40,62</t>
+          <t>12,91; 40,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,5; 38,13</t>
+          <t>15,29; 38,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32,23; 50,91</t>
+          <t>31,5; 51,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,44; 47,03</t>
+          <t>18,54; 47,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,0; 52,88</t>
+          <t>17,93; 54,63</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,92; 52,96</t>
+          <t>6,72; 52,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,68; 62,85</t>
+          <t>23,1; 61,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,25; 73,71</t>
+          <t>30,82; 75,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,09; 49,25</t>
+          <t>9,77; 51,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,43; 53,56</t>
+          <t>16,82; 54,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,14; 45,51</t>
+          <t>15,33; 48,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 54,85</t>
+          <t>7,06; 55,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 54,12</t>
+          <t>6,1; 57,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,78; 45,41</t>
+          <t>16,33; 45,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,38; 46,51</t>
+          <t>21,63; 46,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,67; 56,57</t>
+          <t>23,95; 58,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,46; 46,25</t>
+          <t>9,64; 45,56</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,11; 85,27</t>
+          <t>12,64; 87,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,55; 86,89</t>
+          <t>13,81; 85,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,7</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,82; 100,0</t>
+          <t>19,65; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,0; 66,78</t>
+          <t>16,1; 73,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,64; 80,08</t>
+          <t>17,62; 74,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,01; 90,97</t>
+          <t>30,7; 91,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31,36; 100,0</t>
+          <t>33,38; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,6; 67,68</t>
+          <t>21,97; 68,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20,86; 68,27</t>
+          <t>22,42; 68,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30,51; 80,85</t>
+          <t>29,36; 79,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43,54; 91,49</t>
+          <t>41,29; 91,08</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,53; 30,15</t>
+          <t>12,4; 29,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,9; 42,97</t>
+          <t>25,81; 42,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,97; 51,81</t>
+          <t>28,89; 53,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,7; 56,99</t>
+          <t>27,69; 58,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,05; 39,43</t>
+          <t>22,49; 38,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,24; 40,09</t>
+          <t>24,97; 40,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,16; 57,62</t>
+          <t>35,59; 58,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,69; 38,5</t>
+          <t>17,76; 38,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,43; 32,56</t>
+          <t>20,29; 32,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,05; 39,39</t>
+          <t>26,96; 38,59</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34,97; 51,5</t>
+          <t>36,25; 52,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,69; 42,36</t>
+          <t>24,52; 41,33</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2183</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4995</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3274</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4815</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3109</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4593</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3572</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5515</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>8105</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3440</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>657; 4307</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3147</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2349; 7376</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1281; 6015</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4050</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2673; 6827</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>863; 6794</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1978; 8299</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1393; 7000</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2634; 8587</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4669; 12115</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1869</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2323</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2872</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4571</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3641</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2872</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2616</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7138</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5965</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>576; 4455</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>720; 4860</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>832; 5538</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3004</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2455; 6647</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1165; 7516</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>708; 5869</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>692; 5721</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4379; 9273</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2717; 10248</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4004</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2997</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>630; 4717</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>681; 3323</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2560</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1938; 7384</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3221</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>606; 3929</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>532; 5041</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1948; 7530</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>644; 5814</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2002; 6631</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>871; 5757</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4902</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11855</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4292</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9484</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4683</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>18692</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4329</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7657</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>9585</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>30547</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8620</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>17140</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2407; 8053</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7396; 16837</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1825; 7639</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3399; 18493</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1994; 8123</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13376; 24298</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2063; 7315</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4033; 12569</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>5725; 14272</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>23141; 37997</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5074; 12948</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>9956; 30330</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6987</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7352</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3493</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5374</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6901</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2407</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>7299</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7348</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>13889</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9759</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>10792</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>588; 4551</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4012; 10622</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4238; 10325</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1272; 6711</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2721; 8824</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3620; 11487</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>700; 5496</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1615; 15207</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4070; 11380</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>8866; 18971</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5665; 13780</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3808; 18005</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2177</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2683</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3153</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>4235</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>5587</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5865</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>6918</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>669; 4618</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>681; 4202</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2895</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>804; 4089</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1276; 5856</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1235; 5220</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2195; 6507</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1882; 5640</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2905; 9012</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2677; 8211</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2949; 8015</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>4017; 8861</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>10577</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>27058</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>17865</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>23901</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>23411</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>31484</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>23142</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>28015</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>33988</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>58542</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>41007</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>51916</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>6544; 15609</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>20707; 34466</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>12799; 23747</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>17385; 37000</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>17578; 30173</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>24362; 39458</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>17712; 29016</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>17162; 37214</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>26574; 41974</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>47937; 68617</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>34095; 49534</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>39090; 65894</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,15</t>
+          <t>0,0; 40,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,66; 63,32</t>
+          <t>9,73; 67,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,74</t>
+          <t>0,0; 55,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,11; 69,43</t>
+          <t>22,37; 72,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,16; 52,43</t>
+          <t>10,97; 51,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,04</t>
+          <t>0,0; 47,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,75; 91,32</t>
+          <t>34,41; 83,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 47,63</t>
+          <t>5,81; 44,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,3; 39,03</t>
+          <t>9,36; 38,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,74; 48,96</t>
+          <t>9,72; 47,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,52; 66,91</t>
+          <t>22,32; 66,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,76; 48,68</t>
+          <t>18,7; 50,39</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,8; 52,56</t>
+          <t>6,78; 52,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 59,26</t>
+          <t>9,14; 59,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,57; 63,75</t>
+          <t>14,95; 63,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,17</t>
+          <t>0,0; 40,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,77; 77,92</t>
+          <t>26,84; 83,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,37; 66,85</t>
+          <t>7,92; 62,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 35,8</t>
+          <t>4,46; 38,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 34,1</t>
+          <t>4,08; 34,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,46; 83,55</t>
+          <t>40,23; 87,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,97; 52,71</t>
+          <t>13,08; 51,38</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 57,65</t>
+          <t>7,03; 57,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,97; 53,23</t>
+          <t>13,41; 49,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,52</t>
+          <t>0,0; 20,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,56; 68,4</t>
+          <t>10,64; 69,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 64,9</t>
+          <t>6,72; 60,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,99; 42,51</t>
+          <t>11,03; 42,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 28,6</t>
+          <t>3,2; 29,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,08; 73,14</t>
+          <t>16,64; 72,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 55,74</t>
+          <t>10,04; 58,64</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,83; 46,25</t>
+          <t>13,97; 49,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,47; 48,87</t>
+          <t>23,13; 48,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,12; 46,54</t>
+          <t>11,7; 48,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,0; 76,14</t>
+          <t>13,24; 74,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 40,56</t>
+          <t>9,94; 40,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,29; 62,28</t>
+          <t>33,52; 60,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,83; 66,79</t>
+          <t>14,45; 65,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,91; 40,25</t>
+          <t>13,16; 38,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,29; 38,13</t>
+          <t>15,62; 38,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31,5; 51,72</t>
+          <t>32,61; 51,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,54; 47,32</t>
+          <t>18,49; 46,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,93; 54,63</t>
+          <t>18,35; 54,96</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 52,02</t>
+          <t>7,08; 54,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,1; 61,16</t>
+          <t>21,22; 60,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,82; 75,09</t>
+          <t>31,04; 73,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,77; 51,55</t>
+          <t>8,29; 50,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,82; 54,53</t>
+          <t>16,36; 53,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,33; 48,64</t>
+          <t>15,42; 47,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,06; 55,47</t>
+          <t>7,16; 53,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,1; 57,39</t>
+          <t>6,58; 56,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,33; 45,65</t>
+          <t>16,42; 44,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,63; 46,29</t>
+          <t>22,54; 47,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,95; 58,25</t>
+          <t>24,43; 58,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,64; 45,56</t>
+          <t>10,78; 47,65</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,64; 87,21</t>
+          <t>12,21; 86,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,81; 85,15</t>
+          <t>13,81; 85,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,65; 100,0</t>
+          <t>18,03; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,1; 73,9</t>
+          <t>15,72; 71,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,62; 74,49</t>
+          <t>17,5; 74,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,7; 91,0</t>
+          <t>33,41; 91,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,38; 100,0</t>
+          <t>34,83; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,97; 68,17</t>
+          <t>20,49; 67,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,42; 68,75</t>
+          <t>22,29; 67,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29,36; 79,78</t>
+          <t>29,95; 82,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41,29; 91,08</t>
+          <t>39,96; 91,59</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,4; 29,57</t>
+          <t>12,63; 30,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,81; 42,97</t>
+          <t>25,86; 42,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,89; 53,6</t>
+          <t>29,78; 52,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,69; 58,93</t>
+          <t>27,16; 56,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,49; 38,6</t>
+          <t>22,31; 38,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,97; 40,44</t>
+          <t>24,39; 39,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,59; 58,31</t>
+          <t>35,47; 59,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,76; 38,51</t>
+          <t>19,24; 38,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,29; 32,05</t>
+          <t>20,29; 32,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,96; 38,59</t>
+          <t>27,9; 39,16</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36,25; 52,66</t>
+          <t>35,48; 52,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,52; 41,33</t>
+          <t>24,97; 42,58</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3440</t>
+          <t>0; 4006</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>657; 4307</t>
+          <t>662; 4603</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3147</t>
+          <t>0; 2953</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2349; 7376</t>
+          <t>2376; 7740</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1281; 6015</t>
+          <t>1258; 5936</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4050</t>
+          <t>0; 3568</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2673; 6827</t>
+          <t>2572; 6239</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>863; 6794</t>
+          <t>828; 6418</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1978; 8299</t>
+          <t>1990; 8214</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1393; 7000</t>
+          <t>1389; 6848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2634; 8587</t>
+          <t>2864; 8590</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4669; 12115</t>
+          <t>4654; 12542</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>576; 4455</t>
+          <t>574; 4424</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,47 +2150,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>720; 4860</t>
+          <t>749; 4877</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>832; 5538</t>
+          <t>1299; 5507</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3004</t>
+          <t>0; 3394</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2455; 6647</t>
+          <t>2290; 7099</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1165; 7516</t>
+          <t>890; 7065</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>708; 5869</t>
+          <t>731; 6367</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>692; 5721</t>
+          <t>684; 5859</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4379; 9273</t>
+          <t>4465; 9727</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2717; 10248</t>
+          <t>2543; 9990</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>630; 4717</t>
+          <t>576; 4705</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2363,42 +2363,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1938; 7384</t>
+          <t>1860; 6872</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3221</t>
+          <t>0; 2549</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>606; 3929</t>
+          <t>611; 4005</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>532; 5041</t>
+          <t>522; 4695</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1948; 7530</t>
+          <t>1955; 7576</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>644; 5814</t>
+          <t>650; 6028</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2002; 6631</t>
+          <t>1509; 6547</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>871; 5757</t>
+          <t>1037; 6057</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2407; 8053</t>
+          <t>2431; 8577</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7396; 16837</t>
+          <t>7971; 16561</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1825; 7639</t>
+          <t>1920; 7885</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3399; 18493</t>
+          <t>3215; 18123</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1994; 8123</t>
+          <t>1990; 8110</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13376; 24298</t>
+          <t>13079; 23613</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2063; 7315</t>
+          <t>1583; 7179</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4033; 12569</t>
+          <t>4108; 12175</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5725; 14272</t>
+          <t>5845; 14314</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23141; 37997</t>
+          <t>23959; 37601</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5074; 12948</t>
+          <t>5060; 12771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9956; 30330</t>
+          <t>10187; 30514</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>588; 4551</t>
+          <t>619; 4770</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4012; 10622</t>
+          <t>3685; 10474</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4238; 10325</t>
+          <t>4268; 10159</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1272; 6711</t>
+          <t>1079; 6631</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2721; 8824</t>
+          <t>2647; 8716</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3620; 11487</t>
+          <t>3641; 11123</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>700; 5496</t>
+          <t>709; 5268</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1615; 15207</t>
+          <t>1743; 14886</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4070; 11380</t>
+          <t>4093; 11009</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8866; 18971</t>
+          <t>9237; 19539</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5665; 13780</t>
+          <t>5779; 13832</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3808; 18005</t>
+          <t>4258; 18827</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>669; 4618</t>
+          <t>647; 4562</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>681; 4202</t>
+          <t>681; 4241</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>804; 4089</t>
+          <t>737; 4089</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1276; 5856</t>
+          <t>1246; 5663</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1235; 5220</t>
+          <t>1227; 5223</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2195; 6507</t>
+          <t>2389; 6508</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1882; 5640</t>
+          <t>1965; 5640</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2905; 9012</t>
+          <t>2709; 8864</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2677; 8211</t>
+          <t>2662; 8089</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2949; 8015</t>
+          <t>3009; 8240</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4017; 8861</t>
+          <t>3887; 8911</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6544; 15609</t>
+          <t>6668; 16065</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20707; 34466</t>
+          <t>20746; 34389</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12799; 23747</t>
+          <t>13194; 23476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17385; 37000</t>
+          <t>17052; 35165</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17578; 30173</t>
+          <t>17439; 29805</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24362; 39458</t>
+          <t>23799; 38912</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17712; 29016</t>
+          <t>17651; 29365</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>17162; 37214</t>
+          <t>18594; 37314</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26574; 41974</t>
+          <t>26567; 42528</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47937; 68617</t>
+          <t>49606; 69618</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34095; 49534</t>
+          <t>33380; 48963</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>39090; 65894</t>
+          <t>39814; 67883</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>28,53%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18,54%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>64,41%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22,53%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>13,47%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>32,09%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>13,07%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47,03%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>28,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,54%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,41%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,93</t>
+          <t>11,21; 56,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,73; 67,68</t>
+          <t>0,0; 46,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,11</t>
+          <t>35,01; 90,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,37; 72,86</t>
+          <t>6,31; 46,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,97; 51,73</t>
+          <t>0,0; 39,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,62</t>
+          <t>9,75; 63,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,41; 83,45</t>
+          <t>0,0; 58,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,81; 44,99</t>
+          <t>22,99; 71,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 38,63</t>
+          <t>9,19; 38,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,72; 47,9</t>
+          <t>9,58; 49,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,32; 66,93</t>
+          <t>23,09; 65,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,7; 50,39</t>
+          <t>19,34; 50,51</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33,06%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53,58%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>33,47%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>22,06%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>33,06%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>53,58%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9,83; 64,02</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 43,18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21,94; 77,03</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9,93; 64,76</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6,78; 52,2</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,92; 53,02</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9,14; 59,47</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14,95; 63,39</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 40,87</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,84; 83,21</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,92; 62,85</t>
+          <t>7,84; 57,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,46; 38,84</t>
+          <t>4,3; 39,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 34,92</t>
+          <t>3,96; 35,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40,23; 87,65</t>
+          <t>38,22; 83,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,08; 51,38</t>
+          <t>14,68; 55,69</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28,86%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33,89%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28,12%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>24,29%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>65,06%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>36,04%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>28,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>33,89%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>9,95; 50,0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 25,68</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>10,95; 69,91</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7,05; 67,32</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>7,03; 57,5</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7,42; 57,79</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>20,49; 100,0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>13,41; 49,54</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 20,99</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,64; 69,72</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6,72; 60,44</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,03; 42,77</t>
+          <t>10,62; 42,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 29,65</t>
+          <t>3,26; 28,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,64; 72,21</t>
+          <t>20,02; 71,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,04; 58,64</t>
+          <t>10,3; 59,97</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23,38%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47,91%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39,52%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25,76%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>28,16%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>34,41%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>26,15%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39,05%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,38%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39,52%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 49,26</t>
+          <t>12,84; 43,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,13; 48,06</t>
+          <t>34,96; 60,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,7; 48,05</t>
+          <t>13,99; 64,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,24; 74,62</t>
+          <t>13,52; 42,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 40,5</t>
+          <t>13,77; 47,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,52; 60,53</t>
+          <t>21,63; 47,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,45; 65,54</t>
+          <t>12,3; 47,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,16; 38,99</t>
+          <t>8,91; 43,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,62; 38,24</t>
+          <t>15,5; 38,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32,61; 51,18</t>
+          <t>32,23; 50,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,49; 46,67</t>
+          <t>19,44; 47,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,35; 54,96</t>
+          <t>15,93; 36,52</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33,21%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>29,23%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>24,29%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28,16%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>22,56%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>40,23%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>53,47%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26,83%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>33,21%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>29,23%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>24,29%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,08; 54,52</t>
+          <t>16,43; 53,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,22; 60,31</t>
+          <t>15,14; 45,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,04; 73,89</t>
+          <t>7,1; 54,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,29; 50,93</t>
+          <t>6,37; 53,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,36; 53,87</t>
+          <t>6,92; 52,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,42; 47,1</t>
+          <t>22,68; 62,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 53,16</t>
+          <t>30,25; 73,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,58; 56,18</t>
+          <t>9,82; 50,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,42; 44,16</t>
+          <t>16,78; 45,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,54; 47,68</t>
+          <t>22,38; 46,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,43; 58,47</t>
+          <t>24,67; 56,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,78; 47,65</t>
+          <t>11,61; 46,33</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40,43%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>44,99%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>70,95%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>73,6%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>45,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>44,1%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>27,35%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>65,62%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>40,43%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>44,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,95%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>68,16%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,21; 86,16</t>
+          <t>16,0; 66,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,81; 85,94</t>
+          <t>17,64; 80,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>32,01; 90,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,03; 100,0</t>
+          <t>28,93; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,72; 71,46</t>
+          <t>12,11; 85,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,5; 74,53</t>
+          <t>13,55; 86,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,41; 91,02</t>
+          <t>0,0; 83,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,83; 100,0</t>
+          <t>14,66; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,49; 67,05</t>
+          <t>20,6; 67,68</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,29; 67,73</t>
+          <t>20,86; 68,27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29,95; 82,03</t>
+          <t>30,51; 80,85</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39,96; 91,59</t>
+          <t>39,45; 89,79</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29,95%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>32,27%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>46,5%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30,14%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>20,04%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>33,73%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>40,32%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>38,07%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>29,95%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,5%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,63; 30,43</t>
+          <t>22,05; 39,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,86; 42,87</t>
+          <t>25,24; 40,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,78; 52,99</t>
+          <t>35,16; 57,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,16; 56,01</t>
+          <t>21,25; 39,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,31; 38,13</t>
+          <t>12,53; 30,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,39; 39,88</t>
+          <t>24,9; 42,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,47; 59,01</t>
+          <t>27,97; 51,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,24; 38,61</t>
+          <t>22,96; 42,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,29; 32,48</t>
+          <t>20,43; 32,56</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,9; 39,16</t>
+          <t>27,05; 39,39</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35,48; 52,05</t>
+          <t>34,97; 51,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,97; 42,58</t>
+          <t>23,92; 38,63</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3274</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4815</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1319</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2183</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4995</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3274</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1390</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4815</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>7926</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4006</t>
+          <t>1287; 6532</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>662; 4603</t>
+          <t>0; 3467</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2953</t>
+          <t>2617; 6751</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2376; 7740</t>
+          <t>808; 5933</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1258; 5936</t>
+          <t>0; 3878</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3568</t>
+          <t>663; 4350</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2572; 6239</t>
+          <t>0; 3121</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>828; 6418</t>
+          <t>2476; 7656</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1990; 8214</t>
+          <t>1953; 8150</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1389; 6848</t>
+          <t>1370; 7007</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2864; 8590</t>
+          <t>2964; 8449</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4654; 12542</t>
+          <t>4560; 11909</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,49 +2067,49 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2872</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4571</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3628</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1869</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2567</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2323</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2264</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2872</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4571</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3641</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2872</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>2616</t>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5892</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>854; 5561</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3586</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1872; 6572</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1077; 7020</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>574; 4424</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>586; 4493</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>749; 4877</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1299; 5507</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3394</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2290; 7099</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>890; 7065</t>
+          <t>663; 4865</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>731; 6367</t>
+          <t>705; 6479</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>684; 5859</t>
+          <t>664; 5889</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4465; 9727</t>
+          <t>4241; 9274</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2543; 9990</t>
+          <t>2833; 10749</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1894</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1987</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2162</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4003</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>919</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>2813</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1380; 6936</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3119</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>629; 4016</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>475; 4534</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>576; 4705</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>607; 4728</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>681; 3323</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2560</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1860; 6872</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2549</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>611; 4005</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>522; 4695</t>
+          <t>0; 2395</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1955; 7576</t>
+          <t>1881; 7538</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>650; 6028</t>
+          <t>663; 5819</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1509; 6547</t>
+          <t>1815; 6514</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1037; 6057</t>
+          <t>940; 5474</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4683</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18692</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4329</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7177</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4902</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>11855</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4292</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9484</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4683</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>18692</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4329</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>11894</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2431; 8577</t>
+          <t>2572; 8659</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7971; 16561</t>
+          <t>13639; 23771</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1920; 7885</t>
+          <t>1532; 7069</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3215; 18123</t>
+          <t>3767; 11726</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1990; 8110</t>
+          <t>2397; 8273</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13079; 23613</t>
+          <t>7453; 16368</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1583; 7179</t>
+          <t>2019; 7789</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4108; 12175</t>
+          <t>1731; 8508</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5845; 14314</t>
+          <t>5801; 14272</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23959; 37601</t>
+          <t>23677; 37405</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5060; 12771</t>
+          <t>5320; 12870</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10187; 30514</t>
+          <t>7535; 17270</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5374</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6901</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2407</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1974</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>6987</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>7352</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3493</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>5374</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6901</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2407</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10792</t>
+          <t>9892</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>619; 4770</t>
+          <t>2658; 8666</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3685; 10474</t>
+          <t>3576; 10746</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4268; 10159</t>
+          <t>704; 5435</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1079; 6631</t>
+          <t>1458; 12199</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2647; 8716</t>
+          <t>605; 4633</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3641; 11123</t>
+          <t>3938; 10916</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>709; 5268</t>
+          <t>4160; 10134</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1743; 14886</t>
+          <t>1255; 6409</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4093; 11009</t>
+          <t>4182; 11321</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9237; 19539</t>
+          <t>9172; 19060</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5779; 13832</t>
+          <t>5837; 13384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4258; 18827</t>
+          <t>4140; 16523</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3153</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2383</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2177</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>792</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2683</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3153</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5073</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>6827</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>647; 4562</t>
+          <t>1268; 5292</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>681; 4241</t>
+          <t>1236; 5612</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2895</t>
+          <t>2289; 6504</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>737; 4089</t>
+          <t>1613; 5576</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1246; 5663</t>
+          <t>641; 4515</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1227; 5223</t>
+          <t>669; 4288</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2389; 6508</t>
+          <t>0; 2423</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1965; 5640</t>
+          <t>651; 4440</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2709; 8864</t>
+          <t>2724; 8948</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2662; 8089</t>
+          <t>2491; 8155</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3009; 8240</t>
+          <t>3065; 8122</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3887; 8911</t>
+          <t>3951; 8994</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>23411</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>31484</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>23142</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>26134</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>10577</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>27058</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>17865</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>23901</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>23411</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>31484</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>23142</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>28015</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>51916</t>
+          <t>45244</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6668; 16065</t>
+          <t>17238; 30824</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20746; 34389</t>
+          <t>24624; 39123</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13194; 23476</t>
+          <t>17495; 28676</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17052; 35165</t>
+          <t>18421; 34619</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17439; 29805</t>
+          <t>6614; 15914</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23799; 38912</t>
+          <t>19974; 34467</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17651; 29365</t>
+          <t>12393; 22956</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18594; 37314</t>
+          <t>13376; 24933</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26567; 42528</t>
+          <t>26758; 42632</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49606; 69618</t>
+          <t>48094; 70026</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33380; 48963</t>
+          <t>32891; 48441</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>39814; 67883</t>
+          <t>34684; 56009</t>
         </is>
       </c>
     </row>
